--- a/dados/TC_Principal/Forecast/df_vol_historico.xlsx
+++ b/dados/TC_Principal/Forecast/df_vol_historico.xlsx
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>170</v>
+        <v>419</v>
       </c>
       <c r="D14" t="n">
         <v>2026</v>
@@ -696,7 +696,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1526</v>
+        <v>1365</v>
       </c>
       <c r="D15" t="n">
         <v>2026</v>
@@ -714,7 +714,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>82</v>
+        <v>121</v>
       </c>
       <c r="D16" t="n">
         <v>2026</v>
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="D17" t="n">
         <v>2026</v>
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
         <v>2026</v>
@@ -768,7 +768,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="D19" t="n">
         <v>2026</v>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>374</v>
+        <v>413</v>
       </c>
       <c r="D20" t="n">
         <v>2026</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1120</v>
+        <v>1144</v>
       </c>
       <c r="D21" t="n">
         <v>2026</v>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>218</v>
+        <v>244</v>
       </c>
       <c r="D24" t="n">
         <v>2026</v>
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1958</v>
+        <v>2196</v>
       </c>
       <c r="D25" t="n">
         <v>2026</v>
@@ -894,7 +894,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>154</v>
+        <v>195</v>
       </c>
       <c r="D26" t="n">
         <v>2026</v>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>360</v>
+        <v>455</v>
       </c>
       <c r="D27" t="n">
         <v>2026</v>
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="D28" t="n">
         <v>2026</v>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>200</v>
+        <v>311</v>
       </c>
       <c r="D29" t="n">
         <v>2026</v>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>488</v>
+        <v>514</v>
       </c>
       <c r="D30" t="n">
         <v>2026</v>
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1464</v>
+        <v>1540</v>
       </c>
       <c r="D31" t="n">
         <v>2026</v>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>186</v>
+        <v>216</v>
       </c>
       <c r="D34" t="n">
         <v>2026</v>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1676</v>
+        <v>1944</v>
       </c>
       <c r="D35" t="n">
         <v>2026</v>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>97</v>
+        <v>132</v>
       </c>
       <c r="D36" t="n">
         <v>2026</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>226</v>
+        <v>307</v>
       </c>
       <c r="D37" t="n">
         <v>2026</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>74</v>
+        <v>224</v>
       </c>
       <c r="D38" t="n">
         <v>2026</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>173</v>
+        <v>524</v>
       </c>
       <c r="D39" t="n">
         <v>2026</v>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="D40" t="n">
         <v>2026</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1368</v>
+        <v>1351</v>
       </c>
       <c r="D41" t="n">
         <v>2026</v>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>218</v>
+        <v>275</v>
       </c>
       <c r="D44" t="n">
         <v>2026</v>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1960</v>
+        <v>2479</v>
       </c>
       <c r="D45" t="n">
         <v>2026</v>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="D46" t="n">
         <v>2026</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>277</v>
+        <v>340</v>
       </c>
       <c r="D47" t="n">
         <v>2026</v>
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>86</v>
+        <v>119</v>
       </c>
       <c r="D48" t="n">
         <v>2026</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="D49" t="n">
         <v>2026</v>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>517</v>
+        <v>392</v>
       </c>
       <c r="D50" t="n">
         <v>2026</v>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1551</v>
+        <v>1176</v>
       </c>
       <c r="D51" t="n">
         <v>2026</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>523</v>
+        <v>0</v>
       </c>
       <c r="D52" t="n">
         <v>2026</v>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1220</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>2026</v>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>157</v>
+        <v>330</v>
       </c>
       <c r="D54" t="n">
         <v>2026</v>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1414</v>
+        <v>2971</v>
       </c>
       <c r="D55" t="n">
         <v>2026</v>
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D56" t="n">
         <v>2026</v>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D57" t="n">
         <v>2026</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D58" t="n">
         <v>2026</v>
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="D59" t="n">
         <v>2026</v>
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="D60" t="n">
         <v>2026</v>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>955</v>
+        <v>973</v>
       </c>
       <c r="D61" t="n">
         <v>2026</v>

--- a/dados/TC_Principal/Forecast/df_vol_historico.xlsx
+++ b/dados/TC_Principal/Forecast/df_vol_historico.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>216</v>
+        <v>198</v>
       </c>
       <c r="D34" t="n">
         <v>2026</v>
@@ -1056,7 +1056,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1944</v>
+        <v>1782</v>
       </c>
       <c r="D35" t="n">
         <v>2026</v>
@@ -1074,7 +1074,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>132</v>
+        <v>165</v>
       </c>
       <c r="D36" t="n">
         <v>2026</v>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>307</v>
+        <v>385</v>
       </c>
       <c r="D37" t="n">
         <v>2026</v>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>224</v>
+        <v>145</v>
       </c>
       <c r="D38" t="n">
         <v>2026</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>524</v>
+        <v>339</v>
       </c>
       <c r="D39" t="n">
         <v>2026</v>
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>450</v>
+        <v>479</v>
       </c>
       <c r="D40" t="n">
         <v>2026</v>
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1351</v>
+        <v>1435</v>
       </c>
       <c r="D41" t="n">
         <v>2026</v>
@@ -1218,7 +1218,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="D44" t="n">
         <v>2026</v>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2479</v>
+        <v>2299</v>
       </c>
       <c r="D45" t="n">
         <v>2026</v>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="D46" t="n">
         <v>2026</v>
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="D47" t="n">
         <v>2026</v>
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D48" t="n">
         <v>2026</v>
@@ -1308,7 +1308,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="D49" t="n">
         <v>2026</v>
@@ -1326,7 +1326,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>392</v>
+        <v>442</v>
       </c>
       <c r="D50" t="n">
         <v>2026</v>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1176</v>
+        <v>1326</v>
       </c>
       <c r="D51" t="n">
         <v>2026</v>
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>568</v>
       </c>
       <c r="D52" t="n">
         <v>2026</v>
@@ -1380,7 +1380,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1325</v>
       </c>
       <c r="D53" t="n">
         <v>2026</v>
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>330</v>
+        <v>149</v>
       </c>
       <c r="D54" t="n">
         <v>2026</v>
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2971</v>
+        <v>1336</v>
       </c>
       <c r="D55" t="n">
         <v>2026</v>
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D56" t="n">
         <v>2026</v>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="D57" t="n">
         <v>2026</v>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D58" t="n">
         <v>2026</v>
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="D59" t="n">
         <v>2026</v>
@@ -1506,7 +1506,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D60" t="n">
         <v>2026</v>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>973</v>
+        <v>942</v>
       </c>
       <c r="D61" t="n">
         <v>2026</v>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="D62" t="n">
         <v>2026</v>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2712</v>
+        <v>2701</v>
       </c>
       <c r="D63" t="n">
         <v>2026</v>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="D64" t="n">
         <v>2026</v>
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1189</v>
+        <v>1607</v>
       </c>
       <c r="D65" t="n">
         <v>2026</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>243</v>
+        <v>169</v>
       </c>
       <c r="D66" t="n">
         <v>2026</v>
@@ -1632,7 +1632,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>568</v>
+        <v>394</v>
       </c>
       <c r="D67" t="n">
         <v>2026</v>
@@ -1650,7 +1650,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>287</v>
+        <v>192</v>
       </c>
       <c r="D68" t="n">
         <v>2026</v>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>671</v>
+        <v>448</v>
       </c>
       <c r="D69" t="n">
         <v>2026</v>
@@ -1686,7 +1686,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="D70" t="n">
         <v>2026</v>
@@ -1704,7 +1704,7 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>1438</v>
+        <v>1450</v>
       </c>
       <c r="D71" t="n">
         <v>2026</v>
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1457</v>
+        <v>1614</v>
       </c>
       <c r="D72" t="n">
         <v>2026</v>
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>3398</v>
+        <v>3766</v>
       </c>
       <c r="D73" t="n">
         <v>2026</v>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="D74" t="n">
         <v>2026</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2130</v>
+        <v>1929</v>
       </c>
       <c r="D75" t="n">
         <v>2026</v>
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="D76" t="n">
         <v>2026</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>405</v>
+        <v>363</v>
       </c>
       <c r="D77" t="n">
         <v>2026</v>
@@ -1830,7 +1830,7 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D78" t="n">
         <v>2026</v>
@@ -1848,7 +1848,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="D79" t="n">
         <v>2026</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>617</v>
+        <v>500</v>
       </c>
       <c r="D80" t="n">
         <v>2026</v>
@@ -1884,7 +1884,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>1852</v>
+        <v>1501</v>
       </c>
       <c r="D81" t="n">
         <v>2026</v>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>1593</v>
+        <v>1554</v>
       </c>
       <c r="D82" t="n">
         <v>2026</v>
@@ -1920,7 +1920,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3717</v>
+        <v>3626</v>
       </c>
       <c r="D83" t="n">
         <v>2026</v>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="D84" t="n">
         <v>2026</v>
@@ -1956,7 +1956,7 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1795</v>
+        <v>1592</v>
       </c>
       <c r="D85" t="n">
         <v>2026</v>
@@ -1974,7 +1974,7 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D86" t="n">
         <v>2026</v>
@@ -1992,7 +1992,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>393</v>
+        <v>442</v>
       </c>
       <c r="D87" t="n">
         <v>2026</v>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>140</v>
+        <v>182</v>
       </c>
       <c r="D88" t="n">
         <v>2026</v>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>326</v>
+        <v>426</v>
       </c>
       <c r="D89" t="n">
         <v>2026</v>
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>611</v>
+        <v>488</v>
       </c>
       <c r="D90" t="n">
         <v>2026</v>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>1834</v>
+        <v>1463</v>
       </c>
       <c r="D91" t="n">
         <v>2026</v>
@@ -2082,7 +2082,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>1589</v>
+        <v>1613</v>
       </c>
       <c r="D92" t="n">
         <v>2026</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>3707</v>
+        <v>3763</v>
       </c>
       <c r="D93" t="n">
         <v>2026</v>
@@ -2118,7 +2118,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D94" t="n">
         <v>2026</v>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>1833</v>
+        <v>1871</v>
       </c>
       <c r="D95" t="n">
         <v>2026</v>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>204</v>
+        <v>185</v>
       </c>
       <c r="D96" t="n">
         <v>2026</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>475</v>
+        <v>431</v>
       </c>
       <c r="D97" t="n">
         <v>2026</v>
@@ -2190,7 +2190,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="D98" t="n">
         <v>2026</v>
@@ -2208,7 +2208,7 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>340</v>
+        <v>379</v>
       </c>
       <c r="D99" t="n">
         <v>2026</v>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>563</v>
+        <v>488</v>
       </c>
       <c r="D100" t="n">
         <v>2026</v>
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>1689</v>
+        <v>1462</v>
       </c>
       <c r="D101" t="n">
         <v>2026</v>
@@ -2262,7 +2262,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1466</v>
+        <v>1486</v>
       </c>
       <c r="D102" t="n">
         <v>2026</v>
@@ -2280,7 +2280,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>3419</v>
+        <v>3466</v>
       </c>
       <c r="D103" t="n">
         <v>2026</v>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>148</v>
+        <v>175</v>
       </c>
       <c r="D104" t="n">
         <v>2026</v>
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>1329</v>
+        <v>1575</v>
       </c>
       <c r="D105" t="n">
         <v>2026</v>
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="D106" t="n">
         <v>2026</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>401</v>
+        <v>355</v>
       </c>
       <c r="D107" t="n">
         <v>2026</v>
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="D108" t="n">
         <v>2026</v>
@@ -2388,7 +2388,7 @@
         </is>
       </c>
       <c r="C109" t="n">
-        <v>286</v>
+        <v>367</v>
       </c>
       <c r="D109" t="n">
         <v>2026</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>644</v>
+        <v>486</v>
       </c>
       <c r="D110" t="n">
         <v>2026</v>
@@ -2424,7 +2424,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>1930</v>
+        <v>1456</v>
       </c>
       <c r="D111" t="n">
         <v>2026</v>
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1532</v>
+        <v>1486</v>
       </c>
       <c r="D112" t="n">
         <v>2026</v>
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>3575</v>
+        <v>3466</v>
       </c>
       <c r="D113" t="n">
         <v>2026</v>
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="C114" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="D114" t="n">
         <v>2026</v>
@@ -2496,7 +2496,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1366</v>
+        <v>1454</v>
       </c>
       <c r="D115" t="n">
         <v>2026</v>
@@ -2514,7 +2514,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="D116" t="n">
         <v>2026</v>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="D117" t="n">
         <v>2026</v>
@@ -2550,7 +2550,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="D118" t="n">
         <v>2026</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="C119" t="n">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="D119" t="n">
         <v>2026</v>
@@ -2586,7 +2586,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>689</v>
+        <v>563</v>
       </c>
       <c r="D120" t="n">
         <v>2026</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>2066</v>
+        <v>1689</v>
       </c>
       <c r="D121" t="n">
         <v>2026</v>
